--- a/artfynd/A 14695-2024 artfynd.xlsx
+++ b/artfynd/A 14695-2024 artfynd.xlsx
@@ -2926,10 +2926,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120040119</v>
+        <v>120039823</v>
       </c>
       <c r="B23" t="n">
-        <v>91883</v>
+        <v>91839</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2938,25 +2938,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5448</v>
+        <v>1435</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2969,7 +2969,7 @@
         <v>544358</v>
       </c>
       <c r="R23" t="n">
-        <v>6705945</v>
+        <v>6705940</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3011,7 +3011,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3038,10 +3038,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120039823</v>
+        <v>120040119</v>
       </c>
       <c r="B24" t="n">
-        <v>91839</v>
+        <v>91883</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3050,25 +3050,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1435</v>
+        <v>5448</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3081,7 +3081,7 @@
         <v>544358</v>
       </c>
       <c r="R24" t="n">
-        <v>6705940</v>
+        <v>6705945</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 14695-2024 artfynd.xlsx
+++ b/artfynd/A 14695-2024 artfynd.xlsx
@@ -2455,10 +2455,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120039934</v>
+        <v>120040248</v>
       </c>
       <c r="B19" t="n">
-        <v>91836</v>
+        <v>105009</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2471,34 +2471,43 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4363</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544396</v>
+        <v>544382</v>
       </c>
       <c r="R19" t="n">
-        <v>6705922</v>
+        <v>6705972</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2530,7 +2539,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2540,7 +2549,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2679,10 +2688,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120040239</v>
+        <v>120039909</v>
       </c>
       <c r="B21" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2691,52 +2700,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544382</v>
+        <v>544391</v>
       </c>
       <c r="R21" t="n">
-        <v>6705972</v>
+        <v>6705922</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2768,7 +2763,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2778,7 +2773,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2805,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120040248</v>
+        <v>120040262</v>
       </c>
       <c r="B22" t="n">
-        <v>105009</v>
+        <v>91836</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2821,43 +2816,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>4363</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544382</v>
+        <v>544366</v>
       </c>
       <c r="R22" t="n">
-        <v>6705972</v>
+        <v>6705980</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2889,7 +2875,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2899,7 +2885,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2926,10 +2912,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120039823</v>
+        <v>120039934</v>
       </c>
       <c r="B23" t="n">
-        <v>91839</v>
+        <v>91836</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2938,25 +2924,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1435</v>
+        <v>4363</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2966,10 +2952,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544358</v>
+        <v>544396</v>
       </c>
       <c r="R23" t="n">
-        <v>6705940</v>
+        <v>6705922</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3001,7 +2987,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3011,7 +2997,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3038,10 +3024,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120040119</v>
+        <v>120040239</v>
       </c>
       <c r="B24" t="n">
-        <v>91883</v>
+        <v>97907</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3050,38 +3036,52 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5448</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544358</v>
+        <v>544382</v>
       </c>
       <c r="R24" t="n">
-        <v>6705945</v>
+        <v>6705972</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3271,10 +3271,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120040014</v>
+        <v>120039823</v>
       </c>
       <c r="B26" t="n">
-        <v>97907</v>
+        <v>91839</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3287,48 +3287,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1435</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>544406</v>
+        <v>544358</v>
       </c>
       <c r="R26" t="n">
-        <v>6705944</v>
+        <v>6705940</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3360,7 +3346,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3370,7 +3356,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3397,10 +3383,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120039909</v>
+        <v>120040119</v>
       </c>
       <c r="B27" t="n">
-        <v>90562</v>
+        <v>91883</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3413,21 +3399,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>5448</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3437,10 +3423,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>544391</v>
+        <v>544358</v>
       </c>
       <c r="R27" t="n">
-        <v>6705922</v>
+        <v>6705945</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3472,7 +3458,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3482,7 +3468,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3509,10 +3495,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120040262</v>
+        <v>120040014</v>
       </c>
       <c r="B28" t="n">
-        <v>91836</v>
+        <v>97907</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3521,38 +3507,52 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4363</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>544366</v>
+        <v>544406</v>
       </c>
       <c r="R28" t="n">
-        <v>6705980</v>
+        <v>6705944</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 14695-2024 artfynd.xlsx
+++ b/artfynd/A 14695-2024 artfynd.xlsx
@@ -2576,10 +2576,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120039920</v>
+        <v>120039909</v>
       </c>
       <c r="B20" t="n">
-        <v>90527</v>
+        <v>90562</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2588,25 +2588,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544394</v>
+        <v>544391</v>
       </c>
       <c r="R20" t="n">
-        <v>6705923</v>
+        <v>6705922</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2688,10 +2688,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120039909</v>
+        <v>120039920</v>
       </c>
       <c r="B21" t="n">
-        <v>90562</v>
+        <v>90527</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2700,25 +2700,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2728,10 +2728,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544391</v>
+        <v>544394</v>
       </c>
       <c r="R21" t="n">
-        <v>6705922</v>
+        <v>6705923</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3150,10 +3150,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120040090</v>
+        <v>120039823</v>
       </c>
       <c r="B25" t="n">
-        <v>105009</v>
+        <v>91839</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3162,47 +3162,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221144</v>
+        <v>1435</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544361</v>
+        <v>544358</v>
       </c>
       <c r="R25" t="n">
-        <v>6705950</v>
+        <v>6705940</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3234,7 +3225,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3244,7 +3235,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3271,10 +3262,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120039823</v>
+        <v>120040090</v>
       </c>
       <c r="B26" t="n">
-        <v>91839</v>
+        <v>105009</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3283,38 +3274,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1435</v>
+        <v>221144</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>544358</v>
+        <v>544361</v>
       </c>
       <c r="R26" t="n">
-        <v>6705940</v>
+        <v>6705950</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 14695-2024 artfynd.xlsx
+++ b/artfynd/A 14695-2024 artfynd.xlsx
@@ -2455,10 +2455,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120040248</v>
+        <v>120040119</v>
       </c>
       <c r="B19" t="n">
-        <v>105009</v>
+        <v>91883</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2467,47 +2467,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>5448</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schultz) nom.prov</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544382</v>
+        <v>544358</v>
       </c>
       <c r="R19" t="n">
-        <v>6705972</v>
+        <v>6705945</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2539,7 +2530,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2549,7 +2540,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2576,10 +2567,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120039909</v>
+        <v>120039934</v>
       </c>
       <c r="B20" t="n">
-        <v>90562</v>
+        <v>91836</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2588,25 +2579,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>4363</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2616,7 +2607,7 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544391</v>
+        <v>544396</v>
       </c>
       <c r="R20" t="n">
         <v>6705922</v>
@@ -2651,7 +2642,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2661,7 +2652,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2800,10 +2791,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120040262</v>
+        <v>120040248</v>
       </c>
       <c r="B22" t="n">
-        <v>91836</v>
+        <v>105009</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2816,34 +2807,43 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4363</v>
+        <v>221144</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544366</v>
+        <v>544382</v>
       </c>
       <c r="R22" t="n">
-        <v>6705980</v>
+        <v>6705972</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2912,10 +2912,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120039934</v>
+        <v>120040014</v>
       </c>
       <c r="B23" t="n">
-        <v>91836</v>
+        <v>97907</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2924,38 +2924,52 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4363</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544396</v>
+        <v>544406</v>
       </c>
       <c r="R23" t="n">
-        <v>6705922</v>
+        <v>6705944</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2987,7 +3001,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2997,7 +3011,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3024,10 +3038,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120040239</v>
+        <v>120039823</v>
       </c>
       <c r="B24" t="n">
-        <v>97907</v>
+        <v>91839</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3040,48 +3054,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1435</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544382</v>
+        <v>544358</v>
       </c>
       <c r="R24" t="n">
-        <v>6705972</v>
+        <v>6705940</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3150,10 +3150,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120039823</v>
+        <v>120039942</v>
       </c>
       <c r="B25" t="n">
-        <v>91839</v>
+        <v>97907</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3166,34 +3166,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1435</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544358</v>
+        <v>544399</v>
       </c>
       <c r="R25" t="n">
-        <v>6705940</v>
+        <v>6705923</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3225,7 +3230,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3235,7 +3240,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3262,10 +3267,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120040090</v>
+        <v>120039909</v>
       </c>
       <c r="B26" t="n">
-        <v>105009</v>
+        <v>90562</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3274,47 +3279,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>544361</v>
+        <v>544391</v>
       </c>
       <c r="R26" t="n">
-        <v>6705950</v>
+        <v>6705922</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3346,7 +3342,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3356,7 +3352,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3383,10 +3379,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120040119</v>
+        <v>120040090</v>
       </c>
       <c r="B27" t="n">
-        <v>91883</v>
+        <v>105009</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3395,38 +3391,47 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5448</v>
+        <v>221144</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>544358</v>
+        <v>544361</v>
       </c>
       <c r="R27" t="n">
-        <v>6705945</v>
+        <v>6705950</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3458,7 +3463,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3468,7 +3473,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3495,7 +3500,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120040014</v>
+        <v>120040239</v>
       </c>
       <c r="B28" t="n">
         <v>97907</v>
@@ -3549,10 +3554,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>544406</v>
+        <v>544382</v>
       </c>
       <c r="R28" t="n">
-        <v>6705944</v>
+        <v>6705972</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3584,7 +3589,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3594,7 +3599,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3621,10 +3626,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120039942</v>
+        <v>120040262</v>
       </c>
       <c r="B29" t="n">
-        <v>97907</v>
+        <v>91836</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3633,43 +3638,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>4363</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544399</v>
+        <v>544366</v>
       </c>
       <c r="R29" t="n">
-        <v>6705923</v>
+        <v>6705980</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 14695-2024 artfynd.xlsx
+++ b/artfynd/A 14695-2024 artfynd.xlsx
@@ -2455,10 +2455,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120040119</v>
+        <v>120040090</v>
       </c>
       <c r="B19" t="n">
-        <v>91883</v>
+        <v>105009</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2467,38 +2467,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5448</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544358</v>
+        <v>544361</v>
       </c>
       <c r="R19" t="n">
-        <v>6705945</v>
+        <v>6705950</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2530,7 +2539,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2540,7 +2549,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2567,10 +2576,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120039934</v>
+        <v>120039823</v>
       </c>
       <c r="B20" t="n">
-        <v>91836</v>
+        <v>91839</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2579,25 +2588,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4363</v>
+        <v>1435</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2607,10 +2616,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544396</v>
+        <v>544358</v>
       </c>
       <c r="R20" t="n">
-        <v>6705922</v>
+        <v>6705940</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2642,7 +2651,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2652,7 +2661,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2679,10 +2688,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120039920</v>
+        <v>120040262</v>
       </c>
       <c r="B21" t="n">
-        <v>90527</v>
+        <v>91836</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2695,21 +2704,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>4363</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2719,10 +2728,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544394</v>
+        <v>544366</v>
       </c>
       <c r="R21" t="n">
-        <v>6705923</v>
+        <v>6705980</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2754,7 +2763,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2764,7 +2773,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2791,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120040248</v>
+        <v>120039920</v>
       </c>
       <c r="B22" t="n">
-        <v>105009</v>
+        <v>90527</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2807,43 +2816,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544382</v>
+        <v>544394</v>
       </c>
       <c r="R22" t="n">
-        <v>6705972</v>
+        <v>6705923</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2912,10 +2912,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120040014</v>
+        <v>120040248</v>
       </c>
       <c r="B23" t="n">
-        <v>97907</v>
+        <v>105009</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2924,30 +2924,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2955,21 +2955,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544406</v>
+        <v>544382</v>
       </c>
       <c r="R23" t="n">
-        <v>6705944</v>
+        <v>6705972</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3001,7 +2996,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3011,7 +3006,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3038,10 +3033,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120039823</v>
+        <v>120039934</v>
       </c>
       <c r="B24" t="n">
-        <v>91839</v>
+        <v>91836</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3050,25 +3045,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1435</v>
+        <v>4363</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3078,10 +3073,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544358</v>
+        <v>544396</v>
       </c>
       <c r="R24" t="n">
-        <v>6705940</v>
+        <v>6705922</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3113,7 +3108,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3123,7 +3118,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3150,10 +3145,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120039942</v>
+        <v>120040119</v>
       </c>
       <c r="B25" t="n">
-        <v>97907</v>
+        <v>91883</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3162,43 +3157,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>5448</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544399</v>
+        <v>544358</v>
       </c>
       <c r="R25" t="n">
-        <v>6705923</v>
+        <v>6705945</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3230,7 +3220,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3240,7 +3230,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3379,10 +3369,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120040090</v>
+        <v>120039942</v>
       </c>
       <c r="B27" t="n">
-        <v>105009</v>
+        <v>97907</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3391,35 +3381,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3428,10 +3414,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>544361</v>
+        <v>544399</v>
       </c>
       <c r="R27" t="n">
-        <v>6705950</v>
+        <v>6705923</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3463,7 +3449,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3473,7 +3459,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3626,10 +3612,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120040262</v>
+        <v>120040014</v>
       </c>
       <c r="B29" t="n">
-        <v>91836</v>
+        <v>97907</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3638,38 +3624,52 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4363</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544366</v>
+        <v>544406</v>
       </c>
       <c r="R29" t="n">
-        <v>6705980</v>
+        <v>6705944</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 14695-2024 artfynd.xlsx
+++ b/artfynd/A 14695-2024 artfynd.xlsx
@@ -2576,10 +2576,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120039823</v>
+        <v>120040262</v>
       </c>
       <c r="B20" t="n">
-        <v>91839</v>
+        <v>91836</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2588,25 +2588,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1435</v>
+        <v>4363</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544358</v>
+        <v>544366</v>
       </c>
       <c r="R20" t="n">
-        <v>6705940</v>
+        <v>6705980</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2661,7 +2661,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2688,10 +2688,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120040262</v>
+        <v>120039823</v>
       </c>
       <c r="B21" t="n">
-        <v>91836</v>
+        <v>91839</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2700,25 +2700,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4363</v>
+        <v>1435</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2728,10 +2728,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544366</v>
+        <v>544358</v>
       </c>
       <c r="R21" t="n">
-        <v>6705980</v>
+        <v>6705940</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 14695-2024 artfynd.xlsx
+++ b/artfynd/A 14695-2024 artfynd.xlsx
@@ -2576,10 +2576,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120040262</v>
+        <v>120039823</v>
       </c>
       <c r="B20" t="n">
-        <v>91836</v>
+        <v>91839</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2588,25 +2588,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4363</v>
+        <v>1435</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544366</v>
+        <v>544358</v>
       </c>
       <c r="R20" t="n">
-        <v>6705980</v>
+        <v>6705940</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2661,7 +2661,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2688,10 +2688,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120039823</v>
+        <v>120040262</v>
       </c>
       <c r="B21" t="n">
-        <v>91839</v>
+        <v>91836</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2700,25 +2700,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1435</v>
+        <v>4363</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2728,10 +2728,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544358</v>
+        <v>544366</v>
       </c>
       <c r="R21" t="n">
-        <v>6705940</v>
+        <v>6705980</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 14695-2024 artfynd.xlsx
+++ b/artfynd/A 14695-2024 artfynd.xlsx
@@ -2455,10 +2455,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120040090</v>
+        <v>120039942</v>
       </c>
       <c r="B19" t="n">
-        <v>105009</v>
+        <v>97930</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2467,35 +2467,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2504,10 +2500,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544361</v>
+        <v>544399</v>
       </c>
       <c r="R19" t="n">
-        <v>6705950</v>
+        <v>6705923</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2539,7 +2535,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2549,7 +2545,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2576,10 +2572,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120039823</v>
+        <v>120040248</v>
       </c>
       <c r="B20" t="n">
-        <v>91839</v>
+        <v>105032</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2588,38 +2584,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1435</v>
+        <v>221144</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544358</v>
+        <v>544382</v>
       </c>
       <c r="R20" t="n">
-        <v>6705940</v>
+        <v>6705972</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2651,7 +2656,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2661,7 +2666,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2688,10 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120040262</v>
+        <v>120039920</v>
       </c>
       <c r="B21" t="n">
-        <v>91836</v>
+        <v>90545</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2704,21 +2709,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4363</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2728,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544366</v>
+        <v>544394</v>
       </c>
       <c r="R21" t="n">
-        <v>6705980</v>
+        <v>6705923</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2763,7 +2768,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2773,7 +2778,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2800,10 +2805,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120039920</v>
+        <v>120039909</v>
       </c>
       <c r="B22" t="n">
-        <v>90527</v>
+        <v>90580</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2812,25 +2817,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2840,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544394</v>
+        <v>544391</v>
       </c>
       <c r="R22" t="n">
-        <v>6705923</v>
+        <v>6705922</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2912,10 +2917,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120040248</v>
+        <v>120040262</v>
       </c>
       <c r="B23" t="n">
-        <v>105009</v>
+        <v>91854</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2928,43 +2933,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221144</v>
+        <v>4363</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544382</v>
+        <v>544366</v>
       </c>
       <c r="R23" t="n">
-        <v>6705972</v>
+        <v>6705980</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2996,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3006,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3033,10 +3029,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120039934</v>
+        <v>120040090</v>
       </c>
       <c r="B24" t="n">
-        <v>91836</v>
+        <v>105032</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3049,34 +3045,43 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4363</v>
+        <v>221144</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544396</v>
+        <v>544361</v>
       </c>
       <c r="R24" t="n">
-        <v>6705922</v>
+        <v>6705950</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3108,7 +3113,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3118,7 +3123,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3145,10 +3150,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120040119</v>
+        <v>120040239</v>
       </c>
       <c r="B25" t="n">
-        <v>91883</v>
+        <v>97930</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3157,38 +3162,52 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5448</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544358</v>
+        <v>544382</v>
       </c>
       <c r="R25" t="n">
-        <v>6705945</v>
+        <v>6705972</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3220,7 +3239,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3230,7 +3249,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3257,10 +3276,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120039909</v>
+        <v>120040014</v>
       </c>
       <c r="B26" t="n">
-        <v>90562</v>
+        <v>97930</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3269,38 +3288,52 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>544391</v>
+        <v>544406</v>
       </c>
       <c r="R26" t="n">
-        <v>6705922</v>
+        <v>6705944</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3332,7 +3365,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3342,7 +3375,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3369,10 +3402,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120039942</v>
+        <v>120039934</v>
       </c>
       <c r="B27" t="n">
-        <v>97907</v>
+        <v>91854</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3381,43 +3414,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>4363</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>544399</v>
+        <v>544396</v>
       </c>
       <c r="R27" t="n">
-        <v>6705923</v>
+        <v>6705922</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3449,7 +3477,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3459,7 +3487,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3486,10 +3514,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120040239</v>
+        <v>120040119</v>
       </c>
       <c r="B28" t="n">
-        <v>97907</v>
+        <v>91901</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3498,52 +3526,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>5448</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Schultz) nom.prov</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>544382</v>
+        <v>544358</v>
       </c>
       <c r="R28" t="n">
-        <v>6705972</v>
+        <v>6705945</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3575,7 +3589,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3585,7 +3599,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3612,10 +3626,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120040014</v>
+        <v>120039823</v>
       </c>
       <c r="B29" t="n">
-        <v>97907</v>
+        <v>91857</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3628,48 +3642,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>1435</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544406</v>
+        <v>544358</v>
       </c>
       <c r="R29" t="n">
-        <v>6705944</v>
+        <v>6705940</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 14695-2024 artfynd.xlsx
+++ b/artfynd/A 14695-2024 artfynd.xlsx
@@ -2805,10 +2805,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120039909</v>
+        <v>120040262</v>
       </c>
       <c r="B22" t="n">
-        <v>90580</v>
+        <v>91854</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2817,25 +2817,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>4363</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544391</v>
+        <v>544366</v>
       </c>
       <c r="R22" t="n">
-        <v>6705922</v>
+        <v>6705980</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2917,10 +2917,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120040262</v>
+        <v>120039909</v>
       </c>
       <c r="B23" t="n">
-        <v>91854</v>
+        <v>90580</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2929,25 +2929,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4363</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544366</v>
+        <v>544391</v>
       </c>
       <c r="R23" t="n">
-        <v>6705980</v>
+        <v>6705922</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 14695-2024 artfynd.xlsx
+++ b/artfynd/A 14695-2024 artfynd.xlsx
@@ -2455,10 +2455,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120039942</v>
+        <v>120039934</v>
       </c>
       <c r="B19" t="n">
-        <v>97930</v>
+        <v>91854</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2467,43 +2467,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>4363</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544399</v>
+        <v>544396</v>
       </c>
       <c r="R19" t="n">
-        <v>6705923</v>
+        <v>6705922</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2535,7 +2530,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2545,7 +2540,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2572,10 +2567,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120040248</v>
+        <v>120039909</v>
       </c>
       <c r="B20" t="n">
-        <v>105032</v>
+        <v>90580</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2584,47 +2579,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544382</v>
+        <v>544391</v>
       </c>
       <c r="R20" t="n">
-        <v>6705972</v>
+        <v>6705922</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2656,7 +2642,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2666,7 +2652,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2693,10 +2679,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120039920</v>
+        <v>120039942</v>
       </c>
       <c r="B21" t="n">
-        <v>90545</v>
+        <v>97930</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2705,35 +2691,40 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544394</v>
+        <v>544399</v>
       </c>
       <c r="R21" t="n">
         <v>6705923</v>
@@ -2768,7 +2759,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2778,7 +2769,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2805,10 +2796,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120040262</v>
+        <v>120040090</v>
       </c>
       <c r="B22" t="n">
-        <v>91854</v>
+        <v>105032</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2821,34 +2812,43 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4363</v>
+        <v>221144</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544366</v>
+        <v>544361</v>
       </c>
       <c r="R22" t="n">
-        <v>6705980</v>
+        <v>6705950</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2917,10 +2917,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120039909</v>
+        <v>120040239</v>
       </c>
       <c r="B23" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2929,38 +2929,52 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544391</v>
+        <v>544382</v>
       </c>
       <c r="R23" t="n">
-        <v>6705922</v>
+        <v>6705972</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,7 +3006,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3002,7 +3016,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,10 +3043,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120040090</v>
+        <v>120040119</v>
       </c>
       <c r="B24" t="n">
-        <v>105032</v>
+        <v>91901</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3041,47 +3055,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221144</v>
+        <v>5448</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schultz) nom.prov</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544361</v>
+        <v>544358</v>
       </c>
       <c r="R24" t="n">
-        <v>6705950</v>
+        <v>6705945</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3113,7 +3118,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3123,7 +3128,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3150,10 +3155,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120040239</v>
+        <v>120040248</v>
       </c>
       <c r="B25" t="n">
-        <v>97930</v>
+        <v>105032</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3162,40 +3167,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>överblommad</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3276,10 +3276,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120040014</v>
+        <v>120040262</v>
       </c>
       <c r="B26" t="n">
-        <v>97930</v>
+        <v>91854</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3288,52 +3288,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>4363</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>544406</v>
+        <v>544366</v>
       </c>
       <c r="R26" t="n">
-        <v>6705944</v>
+        <v>6705980</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3365,7 +3351,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3375,7 +3361,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3402,10 +3388,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120039934</v>
+        <v>120040014</v>
       </c>
       <c r="B27" t="n">
-        <v>91854</v>
+        <v>97930</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3414,38 +3400,52 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4363</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>544396</v>
+        <v>544406</v>
       </c>
       <c r="R27" t="n">
-        <v>6705922</v>
+        <v>6705944</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3514,10 +3514,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120040119</v>
+        <v>120039823</v>
       </c>
       <c r="B28" t="n">
-        <v>91901</v>
+        <v>91857</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3526,25 +3526,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5448</v>
+        <v>1435</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3557,7 +3557,7 @@
         <v>544358</v>
       </c>
       <c r="R28" t="n">
-        <v>6705945</v>
+        <v>6705940</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3589,7 +3589,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3626,10 +3626,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120039823</v>
+        <v>120039920</v>
       </c>
       <c r="B29" t="n">
-        <v>91857</v>
+        <v>90545</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3638,25 +3638,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1435</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3666,10 +3666,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544358</v>
+        <v>544394</v>
       </c>
       <c r="R29" t="n">
-        <v>6705940</v>
+        <v>6705923</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 14695-2024 artfynd.xlsx
+++ b/artfynd/A 14695-2024 artfynd.xlsx
@@ -3514,10 +3514,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120039823</v>
+        <v>120039920</v>
       </c>
       <c r="B28" t="n">
-        <v>91857</v>
+        <v>90545</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3526,25 +3526,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1435</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3554,10 +3554,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>544358</v>
+        <v>544394</v>
       </c>
       <c r="R28" t="n">
-        <v>6705940</v>
+        <v>6705923</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3589,7 +3589,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3626,10 +3626,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120039920</v>
+        <v>120039823</v>
       </c>
       <c r="B29" t="n">
-        <v>90545</v>
+        <v>91857</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3638,25 +3638,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>1435</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3666,10 +3666,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544394</v>
+        <v>544358</v>
       </c>
       <c r="R29" t="n">
-        <v>6705923</v>
+        <v>6705940</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 14695-2024 artfynd.xlsx
+++ b/artfynd/A 14695-2024 artfynd.xlsx
@@ -2455,10 +2455,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120039934</v>
+        <v>120039909</v>
       </c>
       <c r="B19" t="n">
-        <v>91854</v>
+        <v>90580</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2467,25 +2467,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4363</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544396</v>
+        <v>544391</v>
       </c>
       <c r="R19" t="n">
         <v>6705922</v>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2567,10 +2567,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120039909</v>
+        <v>120039920</v>
       </c>
       <c r="B20" t="n">
-        <v>90580</v>
+        <v>90545</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2579,25 +2579,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2607,10 +2607,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544391</v>
+        <v>544394</v>
       </c>
       <c r="R20" t="n">
-        <v>6705922</v>
+        <v>6705923</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2679,10 +2679,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120039942</v>
+        <v>120040119</v>
       </c>
       <c r="B21" t="n">
-        <v>97930</v>
+        <v>91901</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2691,43 +2691,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>5448</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544399</v>
+        <v>544358</v>
       </c>
       <c r="R21" t="n">
-        <v>6705923</v>
+        <v>6705945</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2759,7 +2754,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2769,7 +2764,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2796,10 +2791,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120040090</v>
+        <v>120039934</v>
       </c>
       <c r="B22" t="n">
-        <v>105032</v>
+        <v>91854</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2812,43 +2807,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>4363</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544361</v>
+        <v>544396</v>
       </c>
       <c r="R22" t="n">
-        <v>6705950</v>
+        <v>6705922</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2880,7 +2866,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2890,7 +2876,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2917,7 +2903,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120040239</v>
+        <v>120039942</v>
       </c>
       <c r="B23" t="n">
         <v>97930</v>
@@ -2950,16 +2936,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -2971,10 +2948,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544382</v>
+        <v>544399</v>
       </c>
       <c r="R23" t="n">
-        <v>6705972</v>
+        <v>6705923</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3006,7 +2983,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3016,7 +2993,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3043,10 +3020,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120040119</v>
+        <v>120040239</v>
       </c>
       <c r="B24" t="n">
-        <v>91901</v>
+        <v>97930</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3055,38 +3032,52 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5448</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544358</v>
+        <v>544382</v>
       </c>
       <c r="R24" t="n">
-        <v>6705945</v>
+        <v>6705972</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3118,7 +3109,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3128,7 +3119,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3276,10 +3267,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120040262</v>
+        <v>120039823</v>
       </c>
       <c r="B26" t="n">
-        <v>91854</v>
+        <v>91857</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3288,25 +3279,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4363</v>
+        <v>1435</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3316,10 +3307,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>544366</v>
+        <v>544358</v>
       </c>
       <c r="R26" t="n">
-        <v>6705980</v>
+        <v>6705940</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3351,7 +3342,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3361,7 +3352,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3514,10 +3505,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120039920</v>
+        <v>120040262</v>
       </c>
       <c r="B28" t="n">
-        <v>90545</v>
+        <v>91854</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3530,21 +3521,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>4363</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3554,10 +3545,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>544394</v>
+        <v>544366</v>
       </c>
       <c r="R28" t="n">
-        <v>6705923</v>
+        <v>6705980</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3589,7 +3580,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3599,7 +3590,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3626,10 +3617,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120039823</v>
+        <v>120040090</v>
       </c>
       <c r="B29" t="n">
-        <v>91857</v>
+        <v>105032</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3638,38 +3629,47 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1435</v>
+        <v>221144</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544358</v>
+        <v>544361</v>
       </c>
       <c r="R29" t="n">
-        <v>6705940</v>
+        <v>6705950</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 14695-2024 artfynd.xlsx
+++ b/artfynd/A 14695-2024 artfynd.xlsx
@@ -2455,10 +2455,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120039909</v>
+        <v>120040119</v>
       </c>
       <c r="B19" t="n">
-        <v>90580</v>
+        <v>91901</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2471,21 +2471,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>5448</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2495,10 +2495,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544391</v>
+        <v>544358</v>
       </c>
       <c r="R19" t="n">
-        <v>6705922</v>
+        <v>6705945</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2567,10 +2567,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120039920</v>
+        <v>120039934</v>
       </c>
       <c r="B20" t="n">
-        <v>90545</v>
+        <v>91854</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2583,21 +2583,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>4363</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2607,10 +2607,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544394</v>
+        <v>544396</v>
       </c>
       <c r="R20" t="n">
-        <v>6705923</v>
+        <v>6705922</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2679,10 +2679,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120040119</v>
+        <v>120040014</v>
       </c>
       <c r="B21" t="n">
-        <v>91901</v>
+        <v>97930</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2691,38 +2691,52 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5448</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544358</v>
+        <v>544406</v>
       </c>
       <c r="R21" t="n">
-        <v>6705945</v>
+        <v>6705944</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2754,7 +2768,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2764,7 +2778,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2791,10 +2805,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120039934</v>
+        <v>120039942</v>
       </c>
       <c r="B22" t="n">
-        <v>91854</v>
+        <v>97930</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2803,38 +2817,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4363</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544396</v>
+        <v>544399</v>
       </c>
       <c r="R22" t="n">
-        <v>6705922</v>
+        <v>6705923</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2866,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2876,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2903,10 +2922,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120039942</v>
+        <v>120040262</v>
       </c>
       <c r="B23" t="n">
-        <v>97930</v>
+        <v>91854</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2915,43 +2934,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>4363</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544399</v>
+        <v>544366</v>
       </c>
       <c r="R23" t="n">
-        <v>6705923</v>
+        <v>6705980</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2983,7 +2997,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2993,7 +3007,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3020,10 +3034,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120040239</v>
+        <v>120040090</v>
       </c>
       <c r="B24" t="n">
-        <v>97930</v>
+        <v>105032</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3032,30 +3046,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3063,21 +3077,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544382</v>
+        <v>544361</v>
       </c>
       <c r="R24" t="n">
-        <v>6705972</v>
+        <v>6705950</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3109,7 +3118,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3119,7 +3128,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3146,10 +3155,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120040248</v>
+        <v>120039823</v>
       </c>
       <c r="B25" t="n">
-        <v>105032</v>
+        <v>91857</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3158,47 +3167,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221144</v>
+        <v>1435</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544382</v>
+        <v>544358</v>
       </c>
       <c r="R25" t="n">
-        <v>6705972</v>
+        <v>6705940</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3267,10 +3267,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120039823</v>
+        <v>120039920</v>
       </c>
       <c r="B26" t="n">
-        <v>91857</v>
+        <v>90545</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3279,25 +3279,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1435</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>544358</v>
+        <v>544394</v>
       </c>
       <c r="R26" t="n">
-        <v>6705940</v>
+        <v>6705923</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3379,10 +3379,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120040014</v>
+        <v>120039909</v>
       </c>
       <c r="B27" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3391,52 +3391,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>544406</v>
+        <v>544391</v>
       </c>
       <c r="R27" t="n">
-        <v>6705944</v>
+        <v>6705922</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3468,7 +3454,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3478,7 +3464,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3505,10 +3491,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120040262</v>
+        <v>120040239</v>
       </c>
       <c r="B28" t="n">
-        <v>91854</v>
+        <v>97930</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3517,38 +3503,52 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4363</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>544366</v>
+        <v>544382</v>
       </c>
       <c r="R28" t="n">
-        <v>6705980</v>
+        <v>6705972</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3617,7 +3617,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120040090</v>
+        <v>120040248</v>
       </c>
       <c r="B29" t="n">
         <v>105032</v>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3666,10 +3666,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544361</v>
+        <v>544382</v>
       </c>
       <c r="R29" t="n">
-        <v>6705950</v>
+        <v>6705972</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 14695-2024 artfynd.xlsx
+++ b/artfynd/A 14695-2024 artfynd.xlsx
@@ -2455,10 +2455,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120040119</v>
+        <v>120040239</v>
       </c>
       <c r="B19" t="n">
-        <v>91901</v>
+        <v>97930</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2467,38 +2467,52 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5448</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544358</v>
+        <v>544382</v>
       </c>
       <c r="R19" t="n">
-        <v>6705945</v>
+        <v>6705972</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2530,7 +2544,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2540,7 +2554,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2567,10 +2581,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120039934</v>
+        <v>120039823</v>
       </c>
       <c r="B20" t="n">
-        <v>91854</v>
+        <v>91857</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2579,25 +2593,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4363</v>
+        <v>1435</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2607,10 +2621,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544396</v>
+        <v>544358</v>
       </c>
       <c r="R20" t="n">
-        <v>6705922</v>
+        <v>6705940</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2642,7 +2656,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2652,7 +2666,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2679,10 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120040014</v>
+        <v>120040262</v>
       </c>
       <c r="B21" t="n">
-        <v>97930</v>
+        <v>91854</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2691,52 +2705,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>4363</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544406</v>
+        <v>544366</v>
       </c>
       <c r="R21" t="n">
-        <v>6705944</v>
+        <v>6705980</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2922,10 +2922,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120040262</v>
+        <v>120040090</v>
       </c>
       <c r="B23" t="n">
-        <v>91854</v>
+        <v>105032</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2938,34 +2938,43 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4363</v>
+        <v>221144</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544366</v>
+        <v>544361</v>
       </c>
       <c r="R23" t="n">
-        <v>6705980</v>
+        <v>6705950</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2997,7 +3006,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3007,7 +3016,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3034,10 +3043,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120040090</v>
+        <v>120039909</v>
       </c>
       <c r="B24" t="n">
-        <v>105032</v>
+        <v>90580</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3046,47 +3055,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544361</v>
+        <v>544391</v>
       </c>
       <c r="R24" t="n">
-        <v>6705950</v>
+        <v>6705922</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3155,10 +3155,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120039823</v>
+        <v>120039920</v>
       </c>
       <c r="B25" t="n">
-        <v>91857</v>
+        <v>90545</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3167,25 +3167,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1435</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3195,10 +3195,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544358</v>
+        <v>544394</v>
       </c>
       <c r="R25" t="n">
-        <v>6705940</v>
+        <v>6705923</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3267,10 +3267,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120039920</v>
+        <v>120040248</v>
       </c>
       <c r="B26" t="n">
-        <v>90545</v>
+        <v>105032</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3283,34 +3283,43 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>221144</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>544394</v>
+        <v>544382</v>
       </c>
       <c r="R26" t="n">
-        <v>6705923</v>
+        <v>6705972</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3342,7 +3351,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3352,7 +3361,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3379,10 +3388,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120039909</v>
+        <v>120040014</v>
       </c>
       <c r="B27" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3391,38 +3400,52 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>544391</v>
+        <v>544406</v>
       </c>
       <c r="R27" t="n">
-        <v>6705922</v>
+        <v>6705944</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3454,7 +3477,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3464,7 +3487,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3491,10 +3514,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120040239</v>
+        <v>120040119</v>
       </c>
       <c r="B28" t="n">
-        <v>97930</v>
+        <v>91901</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3503,52 +3526,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>5448</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Schultz) nom.prov</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>544382</v>
+        <v>544358</v>
       </c>
       <c r="R28" t="n">
-        <v>6705972</v>
+        <v>6705945</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3580,7 +3589,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3590,7 +3599,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3617,10 +3626,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120040248</v>
+        <v>120039934</v>
       </c>
       <c r="B29" t="n">
-        <v>105032</v>
+        <v>91854</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3633,43 +3642,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221144</v>
+        <v>4363</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544382</v>
+        <v>544396</v>
       </c>
       <c r="R29" t="n">
-        <v>6705972</v>
+        <v>6705922</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 14695-2024 artfynd.xlsx
+++ b/artfynd/A 14695-2024 artfynd.xlsx
@@ -3388,10 +3388,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120040014</v>
+        <v>120040119</v>
       </c>
       <c r="B27" t="n">
-        <v>97930</v>
+        <v>91901</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3400,52 +3400,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>5448</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Schultz) nom.prov</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>544406</v>
+        <v>544358</v>
       </c>
       <c r="R27" t="n">
-        <v>6705944</v>
+        <v>6705945</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3477,7 +3463,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3487,7 +3473,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3514,10 +3500,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120040119</v>
+        <v>120040014</v>
       </c>
       <c r="B28" t="n">
-        <v>91901</v>
+        <v>97930</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3526,38 +3512,52 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5448</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>544358</v>
+        <v>544406</v>
       </c>
       <c r="R28" t="n">
-        <v>6705945</v>
+        <v>6705944</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3589,7 +3589,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 14695-2024 artfynd.xlsx
+++ b/artfynd/A 14695-2024 artfynd.xlsx
@@ -2581,10 +2581,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120039823</v>
+        <v>120039934</v>
       </c>
       <c r="B20" t="n">
-        <v>91857</v>
+        <v>91854</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2593,25 +2593,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1435</v>
+        <v>4363</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2621,10 +2621,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544358</v>
+        <v>544396</v>
       </c>
       <c r="R20" t="n">
-        <v>6705940</v>
+        <v>6705922</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2693,10 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120040262</v>
+        <v>120039920</v>
       </c>
       <c r="B21" t="n">
-        <v>91854</v>
+        <v>90545</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2709,21 +2709,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4363</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544366</v>
+        <v>544394</v>
       </c>
       <c r="R21" t="n">
-        <v>6705980</v>
+        <v>6705923</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2805,10 +2805,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120039942</v>
+        <v>120039823</v>
       </c>
       <c r="B22" t="n">
-        <v>97930</v>
+        <v>91857</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2821,39 +2821,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>1435</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544399</v>
+        <v>544358</v>
       </c>
       <c r="R22" t="n">
-        <v>6705923</v>
+        <v>6705940</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2880,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2895,7 +2890,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2922,10 +2917,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120040090</v>
+        <v>120040262</v>
       </c>
       <c r="B23" t="n">
-        <v>105032</v>
+        <v>91854</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2938,43 +2933,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221144</v>
+        <v>4363</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544361</v>
+        <v>544366</v>
       </c>
       <c r="R23" t="n">
-        <v>6705950</v>
+        <v>6705980</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3006,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3016,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3043,10 +3029,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120039909</v>
+        <v>120040248</v>
       </c>
       <c r="B24" t="n">
-        <v>90580</v>
+        <v>105032</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3055,38 +3041,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544391</v>
+        <v>544382</v>
       </c>
       <c r="R24" t="n">
-        <v>6705922</v>
+        <v>6705972</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3118,7 +3113,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3128,7 +3123,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3155,10 +3150,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120039920</v>
+        <v>120039942</v>
       </c>
       <c r="B25" t="n">
-        <v>90545</v>
+        <v>97930</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3167,35 +3162,40 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544394</v>
+        <v>544399</v>
       </c>
       <c r="R25" t="n">
         <v>6705923</v>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3267,7 +3267,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120040248</v>
+        <v>120040090</v>
       </c>
       <c r="B26" t="n">
         <v>105032</v>
@@ -3302,7 +3302,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>544382</v>
+        <v>544361</v>
       </c>
       <c r="R26" t="n">
-        <v>6705972</v>
+        <v>6705950</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3388,10 +3388,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120040119</v>
+        <v>120039909</v>
       </c>
       <c r="B27" t="n">
-        <v>91901</v>
+        <v>90580</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3404,21 +3404,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5448</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3428,10 +3428,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>544358</v>
+        <v>544391</v>
       </c>
       <c r="R27" t="n">
-        <v>6705945</v>
+        <v>6705922</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3500,10 +3500,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120040014</v>
+        <v>120040119</v>
       </c>
       <c r="B28" t="n">
-        <v>97930</v>
+        <v>91901</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3512,52 +3512,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>5448</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Schultz) nom.prov</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>544406</v>
+        <v>544358</v>
       </c>
       <c r="R28" t="n">
-        <v>6705944</v>
+        <v>6705945</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3589,7 +3575,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3599,7 +3585,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3626,10 +3612,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120039934</v>
+        <v>120040014</v>
       </c>
       <c r="B29" t="n">
-        <v>91854</v>
+        <v>97930</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3638,38 +3624,52 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4363</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544396</v>
+        <v>544406</v>
       </c>
       <c r="R29" t="n">
-        <v>6705922</v>
+        <v>6705944</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 14695-2024 artfynd.xlsx
+++ b/artfynd/A 14695-2024 artfynd.xlsx
@@ -2455,10 +2455,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120040239</v>
+        <v>120039909</v>
       </c>
       <c r="B19" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2467,52 +2467,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544382</v>
+        <v>544391</v>
       </c>
       <c r="R19" t="n">
-        <v>6705972</v>
+        <v>6705922</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2544,7 +2530,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2554,7 +2540,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2581,10 +2567,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120039934</v>
+        <v>120040239</v>
       </c>
       <c r="B20" t="n">
-        <v>91854</v>
+        <v>97930</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2593,38 +2579,52 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4363</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544396</v>
+        <v>544382</v>
       </c>
       <c r="R20" t="n">
-        <v>6705922</v>
+        <v>6705972</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2693,10 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120039920</v>
+        <v>120039942</v>
       </c>
       <c r="B21" t="n">
-        <v>90545</v>
+        <v>97930</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2705,35 +2705,40 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544394</v>
+        <v>544399</v>
       </c>
       <c r="R21" t="n">
         <v>6705923</v>
@@ -2768,7 +2773,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2778,7 +2783,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2805,10 +2810,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120039823</v>
+        <v>120040014</v>
       </c>
       <c r="B22" t="n">
-        <v>91857</v>
+        <v>97930</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2821,34 +2826,48 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1435</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544358</v>
+        <v>544406</v>
       </c>
       <c r="R22" t="n">
-        <v>6705940</v>
+        <v>6705944</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2880,7 +2899,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2890,7 +2909,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2917,7 +2936,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120040262</v>
+        <v>120039934</v>
       </c>
       <c r="B23" t="n">
         <v>91854</v>
@@ -2957,10 +2976,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544366</v>
+        <v>544396</v>
       </c>
       <c r="R23" t="n">
-        <v>6705980</v>
+        <v>6705922</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,7 +3011,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3002,7 +3021,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,7 +3048,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120040248</v>
+        <v>120040090</v>
       </c>
       <c r="B24" t="n">
         <v>105032</v>
@@ -3064,7 +3083,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3078,10 +3097,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544382</v>
+        <v>544361</v>
       </c>
       <c r="R24" t="n">
-        <v>6705972</v>
+        <v>6705950</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3113,7 +3132,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3123,7 +3142,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3150,10 +3169,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120039942</v>
+        <v>120040262</v>
       </c>
       <c r="B25" t="n">
-        <v>97930</v>
+        <v>91854</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3162,43 +3181,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>4363</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544399</v>
+        <v>544366</v>
       </c>
       <c r="R25" t="n">
-        <v>6705923</v>
+        <v>6705980</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3230,7 +3244,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3240,7 +3254,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3267,10 +3281,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120040090</v>
+        <v>120040119</v>
       </c>
       <c r="B26" t="n">
-        <v>105032</v>
+        <v>91901</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3279,47 +3293,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221144</v>
+        <v>5448</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schultz) nom.prov</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>544361</v>
+        <v>544358</v>
       </c>
       <c r="R26" t="n">
-        <v>6705950</v>
+        <v>6705945</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3351,7 +3356,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3361,7 +3366,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3388,10 +3393,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120039909</v>
+        <v>120040248</v>
       </c>
       <c r="B27" t="n">
-        <v>90580</v>
+        <v>105032</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3400,38 +3405,47 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>544391</v>
+        <v>544382</v>
       </c>
       <c r="R27" t="n">
-        <v>6705922</v>
+        <v>6705972</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3463,7 +3477,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3473,7 +3487,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3500,10 +3514,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120040119</v>
+        <v>120039823</v>
       </c>
       <c r="B28" t="n">
-        <v>91901</v>
+        <v>91857</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3512,25 +3526,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5448</v>
+        <v>1435</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3543,7 +3557,7 @@
         <v>544358</v>
       </c>
       <c r="R28" t="n">
-        <v>6705945</v>
+        <v>6705940</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3575,7 +3589,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3585,7 +3599,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3612,10 +3626,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120040014</v>
+        <v>120039920</v>
       </c>
       <c r="B29" t="n">
-        <v>97930</v>
+        <v>90545</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3624,52 +3638,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kalvbäckens gruva, Kalvbäckens gruva, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544406</v>
+        <v>544394</v>
       </c>
       <c r="R29" t="n">
-        <v>6705944</v>
+        <v>6705923</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD29" t="b">
